--- a/Literature Review.xlsx
+++ b/Literature Review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apermesa\Documents\光追音频\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apermesa\Documents\Raytraced Audio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD7E21D-2C8B-498F-A9F5-DE5BCBBB3FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459F0DA-4BA5-4B86-9764-F4C0B1F2A904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>12378-26022-1PB</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +51,6 @@
   </si>
   <si>
     <t>Keywords</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Optimization, attention</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -74,8 +70,51 @@
   <si>
     <t>合理利用并观察玩家的注意力以平衡性能和空间音频准确度
 空间音频包括声源定位和空间化
-每20毫秒更新一次脉冲响应
-游戏画质接近显示，声音模拟却进步缓慢</t>
+每20毫秒更新一次脉冲响应，即50赫兹的刷新率，可以实现接近无法分辨的精度
+游戏画质接近现实，声音模拟却进步缓慢
+使用蒙特卡洛方法获得空间的脉冲响应，尤其是散射反射
+用Diffuse Rain模型大幅降低射线数量
+若声源没有方向性，则射线分布均匀随机；否则更改射线分布的PDF
+提高更新频率以降低每次更新时使用的射线个数，若玩家不动，则更新时增加新射线
+根据声速和声音频段确定半波长，即最小距离精度，再根据玩家移动速度确定时间分辨率
+新增的额外射线会使总能量超过单位值，因此需要能量标准化
+问题：更新多次后重设回原来状态会有割裂的质量差别，或许可用Moving Average解决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000216</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The number of necessary rays in geometrically based simulations using the diffuse rain technique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimization, theory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用Diffuse Rain模型大幅降低射线数量
+平均减少29%的射线数量，效果与纯光追一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physically Based Real-Time Auralization of Interactive Virtual Environments</t>
+  </si>
+  <si>
+    <t>3875</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Theory, practice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2011年的虚拟空间音频模拟博士论文</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -420,11 +459,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="69.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="82" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="76.83203125" style="1" customWidth="1"/>
     <col min="5" max="16384" width="8.6640625" style="1"/>
@@ -441,7 +480,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="42" x14ac:dyDescent="0.3">
@@ -452,13 +491,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -466,10 +505,38 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Literature Review.xlsx
+++ b/Literature Review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apermesa\Documents\Raytraced Audio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apermesa\Documents\GitHub\Raytraced-Audio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459F0DA-4BA5-4B86-9764-F4C0B1F2A904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD40AE63-95F5-45EB-B98C-292E3E287E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -122,17 +122,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -140,7 +140,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -181,7 +181,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -460,16 +460,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="82" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="76.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.9296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="76.796875" style="1" customWidth="1"/>
     <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="21">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -483,7 +483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="154" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="171">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -511,7 +511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -525,7 +525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>

--- a/Literature Review.xlsx
+++ b/Literature Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apermesa\Documents\GitHub\Raytraced-Audio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD40AE63-95F5-45EB-B98C-292E3E287E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0691B0-C9F3-456A-8E3C-CEB5EF89C34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>12378-26022-1PB</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,6 +116,19 @@
   <si>
     <t>2011年的虚拟空间音频模拟博士论文</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D Audio_</t>
+  </si>
+  <si>
+    <t>3D Audio</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>第三章：提出过程化音频概念，声音效果实时渲染
+6DOF概念，玩家可以移动三轴，而且可以在任意二轴之间旋转（XR）</t>
   </si>
 </sst>
 </file>
@@ -459,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.796875" style="1" customWidth="1"/>
@@ -539,6 +552,20 @@
         <v>19</v>
       </c>
     </row>
+    <row r="6" spans="1:4" ht="28.5">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Literature Review.xlsx
+++ b/Literature Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apermesa\Documents\GitHub\Raytraced-Audio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0691B0-C9F3-456A-8E3C-CEB5EF89C34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF1FBE8-6C5C-4DA1-BEE7-194C6643D215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,6 +68,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>000216</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The number of necessary rays in geometrically based simulations using the diffuse rain technique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimization, theory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用Diffuse Rain模型大幅降低射线数量
+平均减少29%的射线数量，效果与纯光追一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physically Based Real-Time Auralization of Interactive Virtual Environments</t>
+  </si>
+  <si>
+    <t>3875</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Theory, practice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2011年的虚拟空间音频模拟博士论文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D Audio_</t>
+  </si>
+  <si>
+    <t>3D Audio</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>第三章：提出过程化音频概念，声音效果实时渲染
+6DOF概念，玩家可以移动三轴，而且可以在任意二轴之间旋转（XR）</t>
+  </si>
+  <si>
     <t>合理利用并观察玩家的注意力以平衡性能和空间音频准确度
 空间音频包括声源定位和空间化
 每20毫秒更新一次脉冲响应，即50赫兹的刷新率，可以实现接近无法分辨的精度
@@ -79,56 +128,6 @@
 根据声速和声音频段确定半波长，即最小距离精度，再根据玩家移动速度确定时间分辨率
 新增的额外射线会使总能量超过单位值，因此需要能量标准化
 问题：更新多次后重设回原来状态会有割裂的质量差别，或许可用Moving Average解决</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>000216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>The number of necessary rays in geometrically based simulations using the diffuse rain technique</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Optimization</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Optimization, theory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用Diffuse Rain模型大幅降低射线数量
-平均减少29%的射线数量，效果与纯光追一样</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physically Based Real-Time Auralization of Interactive Virtual Environments</t>
-  </si>
-  <si>
-    <t>3875</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Theory, practice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2011年的虚拟空间音频模拟博士论文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3D Audio_</t>
-  </si>
-  <si>
-    <t>3D Audio</t>
-  </si>
-  <si>
-    <t>Book</t>
-  </si>
-  <si>
-    <t>第三章：提出过程化音频概念，声音效果实时渲染
-6DOF概念，玩家可以移动三轴，而且可以在任意二轴之间旋转（XR）</t>
   </si>
 </sst>
 </file>
@@ -518,52 +517,52 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.5">
       <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
